--- a/data/SchülerNoten.xlsx
+++ b/data/SchülerNoten.xlsx
@@ -1,26 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29711"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gollnickdatasolutions-my.sharepoint.com/personal/bertgollnick_gollnickdatasolutions_onmicrosoft_com/Documents/Projects/Bildungsurlaub/KIfürJobUndAlltag/Inhalte/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="73" documentId="8_{4A567EC4-FA63-48FC-92AD-44112C065680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3FA57C2-C307-4E04-9498-16EF83DD6D53}"/>
+  <xr:revisionPtr revIDLastSave="145" documentId="8_{4A567EC4-FA63-48FC-92AD-44112C065680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9317C3B0-1CD8-48B4-B78A-7D63FF888B4D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3EABB142-B400-4C38-9C07-8BEF67FD9399}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{3EABB142-B400-4C38-9C07-8BEF67FD9399}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
-    <sheet name="Tabelle2" sheetId="2" r:id="rId2"/>
-    <sheet name="GPT cache" sheetId="3" state="veryHidden" r:id="rId3"/>
-    <sheet name="Tabelle4" sheetId="5" r:id="rId4"/>
+    <sheet name="GPT cache" sheetId="3" state="veryHidden" r:id="rId2"/>
+    <sheet name="Auswertung" sheetId="6" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="2160" r:id="rId5"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -64,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="55">
   <si>
     <t>Student ID</t>
   </si>
@@ -186,15 +185,6 @@
     <t>Scarlett Green</t>
   </si>
   <si>
-    <t>Fach</t>
-  </si>
-  <si>
-    <t>Note</t>
-  </si>
-  <si>
-    <t>A‑</t>
-  </si>
-  <si>
     <t>{"hash":"ac2027851772b8defd0467014ee96c531af38f14853fc423b40b16c5f1967349","version":1,"value":"[[\"Historia\"]]"}</t>
   </si>
   <si>
@@ -216,17 +206,35 @@
     <t>{"hash":"8cce02276f91e464bab98cf48d50d550fada4efb856ff653471006d8cc6757a3","version":1,"value":"[[\"Matemáticas\"]]"}</t>
   </si>
   <si>
-    <t>Mittelwert von Notenwert</t>
-  </si>
-  <si>
     <t>Gesamtergebnis</t>
+  </si>
+  <si>
+    <t>Vorname</t>
+  </si>
+  <si>
+    <t>Nachname</t>
+  </si>
+  <si>
+    <t>📊 Notenübersicht nach Grade</t>
+  </si>
+  <si>
+    <t>Anzahl Schüler und Summe Notenwert je Grade (aus Tabelle1)</t>
+  </si>
+  <si>
+    <t>Zeilenbeschriftungen</t>
+  </si>
+  <si>
+    <t>Anzahl Schüler</t>
+  </si>
+  <si>
+    <t>Summe Notenwert</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -247,13 +255,56 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF1F2D3D"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F2D3D"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF1F2D3D"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F2D3D"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3F6FA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8EEF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="10">
@@ -379,7 +430,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -411,12 +462,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="18">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -599,13 +662,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="medium">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="medium">
           <color rgb="FF000000"/>
         </left>
@@ -615,6 +671,13 @@
         <top style="medium">
           <color rgb="FF000000"/>
         </top>
+        <bottom style="medium">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <bottom style="medium">
           <color rgb="FF000000"/>
         </bottom>
@@ -638,7 +701,7 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
           <color rgb="FF000000"/>
         </left>
@@ -648,6 +711,42 @@
         <top/>
         <bottom/>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1F2D3D"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1F2D3D"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE8EEF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE8EEF7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -676,11 +775,36 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[SchülerNoten.xlsx]Tabelle4!PivotTable1</c:name>
-    <c:fmtId val="0"/>
+    <c:name>[SchülerNoten.xlsx]Auswertung!NotenPivot</c:name>
+    <c:fmtId val="1"/>
   </c:pivotSource>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="de-DE"/>
+              <a:t>Schüler je Grade</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -754,7 +878,63 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-DE"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-DE"/>
             </a:p>
           </c:txPr>
           <c:showLegendKey val="0"/>
@@ -772,7 +952,7 @@
     <c:plotArea>
       <c:layout/>
       <c:barChart>
-        <c:barDir val="bar"/>
+        <c:barDir val="col"/>
         <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
@@ -780,11 +960,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Tabelle4!$B$2</c:f>
+              <c:f>Auswertung!$B$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Ergebnis</c:v>
+                  <c:v>Anzahl Schüler</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -801,66 +981,155 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Tabelle4!$A$3:$A$10</c:f>
+              <c:f>Auswertung!$A$5:$A$12</c:f>
               <c:strCache>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>Biology</c:v>
+                  <c:v>A</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Chemistry</c:v>
+                  <c:v>A-</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Computer Science</c:v>
+                  <c:v>B</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>History</c:v>
+                  <c:v>B-</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Literature</c:v>
+                  <c:v>B+</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Mathematics</c:v>
+                  <c:v>C</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>Physics</c:v>
+                  <c:v>C+</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Tabelle4!$B$3:$B$10</c:f>
+              <c:f>Auswertung!$B$5:$B$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>13.5</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>11.333333333333334</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>14</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>12.333333333333334</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>12</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>13.75</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>13.333333333333334</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-6234-4F96-9916-18A624702DC8}"/>
+              <c16:uniqueId val="{00000000-B566-4DA0-81B6-0A77A757E797}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Auswertung!$C$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Summe Notenwert</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Auswertung!$A$5:$A$12</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>A</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>A-</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>B</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>B-</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>B+</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>C</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>C+</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Auswertung!$C$5:$C$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-B566-4DA0-81B6-0A77A757E797}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -872,22 +1141,22 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="33"/>
-        <c:overlap val="-30"/>
-        <c:axId val="1088892703"/>
-        <c:axId val="1088888383"/>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1089549728"/>
+        <c:axId val="1089546848"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1088892703"/>
+        <c:axId val="1089549728"/>
         <c:scaling>
-          <c:orientation val="maxMin"/>
+          <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
-        <c:axPos val="l"/>
+        <c:axPos val="b"/>
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
@@ -905,7 +1174,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="de-DE"/>
-                  <a:t>Class</a:t>
+                  <a:t>Grade</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -919,7 +1188,7 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
@@ -976,7 +1245,7 @@
             <a:endParaRPr lang="en-DE"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1088888383"/>
+        <c:crossAx val="1089546848"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -984,12 +1253,12 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1088888383"/>
+        <c:axId val="1089546848"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
-        <c:axPos val="b"/>
+        <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
@@ -1007,7 +1276,7 @@
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
@@ -1025,7 +1294,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="de-DE"/>
-                  <a:t>Notenwert</a:t>
+                  <a:t>Anzahl / Summe</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -1039,7 +1308,7 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
@@ -1090,8 +1359,8 @@
             <a:endParaRPr lang="en-DE"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1088892703"/>
-        <c:crosses val="max"/>
+        <c:crossAx val="1089549728"/>
+        <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
@@ -1102,6 +1371,37 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -1149,6 +1449,8 @@
         <c14:dropZoneFilter val="1"/>
         <c14:dropZoneCategories val="1"/>
         <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
       </c14:pivotOptions>
     </c:ext>
     <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
@@ -1201,7 +1503,7 @@
 </file>
 
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -1405,23 +1707,22 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -1526,8 +1827,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -1659,20 +1960,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -1709,23 +2009,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Diagramm 1" descr="Diagrammtyp: Balken (gruppiert). &#10;&#10;Beschreibung automatisch generiert.">
+        <xdr:cNvPr id="3" name="Diagramm 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B006E39C-E41A-8B8D-0FFB-90BD39EE04B8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E87703D-71CF-2761-3F2E-74DA8DFBFB3F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1747,11 +2047,11 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Bert Gollnick" refreshedDate="46040.393645949072" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="20" xr:uid="{3BEF9971-7E5C-4F8C-B712-FDAB16C1B747}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Bert Gollnick" refreshedDate="46086.659983101854" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="20" xr:uid="{AB059FFA-5E9C-4D0C-8B77-C2296CC125AE}">
   <cacheSource type="worksheet">
-    <worksheetSource name="Tabelle1"/>
+    <worksheetSource ref="A1:H21" sheet="Tabelle1"/>
   </cacheSource>
-  <cacheFields count="7">
+  <cacheFields count="8">
     <cacheField name="Student ID" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="101" maxValue="120"/>
     </cacheField>
@@ -1759,27 +2059,30 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="Class" numFmtId="0">
-      <sharedItems count="7">
-        <s v="Mathematics"/>
-        <s v="History"/>
-        <s v="Physics"/>
-        <s v="Literature"/>
-        <s v="Chemistry"/>
-        <s v="Biology"/>
-        <s v="Computer Science"/>
-      </sharedItems>
+      <sharedItems/>
     </cacheField>
     <cacheField name="Grade" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="7">
+        <s v="A"/>
+        <s v="B+"/>
+        <s v="A-"/>
+        <s v="B"/>
+        <s v="C+"/>
+        <s v="B-"/>
+        <s v="C"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Class (Espaniol)" numFmtId="0">
       <sharedItems/>
     </cacheField>
-    <cacheField name="Klassenvergleich" numFmtId="0">
+    <cacheField name="Notenwert" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="9" maxValue="15"/>
+    </cacheField>
+    <cacheField name="Vorname" numFmtId="0">
       <sharedItems/>
     </cacheField>
-    <cacheField name="Notenwert" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="9" maxValue="15"/>
+    <cacheField name="Nachname" numFmtId="0">
+      <sharedItems/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -1795,211 +2098,232 @@
   <r>
     <n v="101"/>
     <s v="Liam Miller"/>
+    <s v="Mathematics"/>
     <x v="0"/>
-    <s v="A"/>
     <s v="Matemáticas"/>
-    <s v="Keine Übereinstimmung"/>
     <n v="15"/>
+    <s v="Liam"/>
+    <s v="Miller"/>
   </r>
   <r>
     <n v="102"/>
     <s v="Sophia Chen"/>
+    <s v="History"/>
     <x v="1"/>
-    <s v="B+"/>
     <s v="Historia"/>
-    <s v="Keine Übereinstimmung"/>
     <n v="13"/>
+    <s v="Sophia"/>
+    <s v="Chen"/>
   </r>
   <r>
     <n v="103"/>
     <s v="Noah Garcia"/>
+    <s v="Physics"/>
     <x v="2"/>
-    <s v="A-"/>
     <s v="Física"/>
-    <s v="Keine Übereinstimmung"/>
     <n v="14"/>
+    <s v="Noah"/>
+    <s v="Garcia"/>
   </r>
   <r>
     <n v="104"/>
     <s v="Emma Wilson"/>
+    <s v="Literature"/>
     <x v="3"/>
-    <s v="B"/>
     <s v="Literatura"/>
-    <s v="Keine Übereinstimmung"/>
     <n v="12"/>
+    <s v="Emma"/>
+    <s v="Wilson"/>
   </r>
   <r>
     <n v="105"/>
     <s v="Oliver Brown"/>
+    <s v="Chemistry"/>
     <x v="4"/>
-    <s v="C+"/>
     <s v="Química"/>
-    <s v="Keine Übereinstimmung"/>
     <n v="10"/>
+    <s v="Oliver"/>
+    <s v="Brown"/>
   </r>
   <r>
     <n v="106"/>
     <s v="Ava Martinez"/>
-    <x v="0"/>
-    <s v="B-"/>
+    <s v="Mathematics"/>
+    <x v="5"/>
     <s v="Matemáticas"/>
-    <s v="Keine Übereinstimmung"/>
     <n v="11"/>
+    <s v="Ava"/>
+    <s v="Martinez"/>
   </r>
   <r>
     <n v="107"/>
     <s v="Lucas Taylor"/>
-    <x v="5"/>
-    <s v="A"/>
+    <s v="Biology"/>
+    <x v="0"/>
     <s v="Biología"/>
-    <s v="Keine Übereinstimmung"/>
     <n v="15"/>
+    <s v="Lucas"/>
+    <s v="Taylor"/>
   </r>
   <r>
     <n v="108"/>
     <s v="Mia Anderson"/>
-    <x v="1"/>
-    <s v="A-"/>
+    <s v="History"/>
+    <x v="2"/>
     <s v="Historia"/>
-    <s v="Keine Übereinstimmung"/>
     <n v="14"/>
+    <s v="Mia"/>
+    <s v="Anderson"/>
   </r>
   <r>
     <n v="109"/>
     <s v="Ethan Thomas"/>
-    <x v="2"/>
-    <s v="B"/>
+    <s v="Physics"/>
+    <x v="3"/>
     <s v="Física"/>
-    <s v="Keine Übereinstimmung"/>
     <n v="12"/>
+    <s v="Ethan"/>
+    <s v="Thomas"/>
   </r>
   <r>
     <n v="110"/>
     <s v="Isabella Moore"/>
-    <x v="6"/>
-    <s v="A"/>
+    <s v="Computer Science"/>
+    <x v="0"/>
     <s v="Ciencias de la Computación"/>
-    <s v="Keine Übereinstimmung"/>
     <n v="15"/>
+    <s v="Isabella"/>
+    <s v="Moore"/>
   </r>
   <r>
     <n v="111"/>
     <s v="Mason Jackson"/>
-    <x v="3"/>
-    <s v="C"/>
+    <s v="Literature"/>
+    <x v="6"/>
     <s v="Literatura"/>
-    <s v="Keine Übereinstimmung"/>
     <n v="9"/>
+    <s v="Mason"/>
+    <s v="Jackson"/>
   </r>
   <r>
     <n v="112"/>
     <s v="Charlotte White"/>
-    <x v="4"/>
-    <s v="B+"/>
+    <s v="Chemistry"/>
+    <x v="1"/>
     <s v="Química"/>
-    <s v="Keine Übereinstimmung"/>
     <n v="13"/>
+    <s v="Charlotte"/>
+    <s v="White"/>
   </r>
   <r>
     <n v="113"/>
     <s v="James Harris"/>
+    <s v="Mathematics"/>
     <x v="0"/>
-    <s v="A"/>
     <s v="Matemáticas"/>
-    <s v="Keine Übereinstimmung"/>
     <n v="15"/>
+    <s v="James"/>
+    <s v="Harris"/>
   </r>
   <r>
     <n v="114"/>
     <s v="Amelia Martin"/>
-    <x v="5"/>
-    <s v="B"/>
+    <s v="Biology"/>
+    <x v="3"/>
     <s v="Biología"/>
-    <s v="Keine Übereinstimmung"/>
     <n v="12"/>
+    <s v="Amelia"/>
+    <s v="Martin"/>
   </r>
   <r>
     <n v="115"/>
     <s v="Benjamin Thompson"/>
+    <s v="Physics"/>
     <x v="2"/>
-    <s v="A-"/>
     <s v="Física"/>
-    <s v="Keine Übereinstimmung"/>
     <n v="14"/>
+    <s v="Benjamin"/>
+    <s v="Thompson"/>
   </r>
   <r>
     <n v="116"/>
     <s v="Harper Lee"/>
-    <x v="6"/>
-    <s v="B+"/>
+    <s v="Computer Science"/>
+    <x v="1"/>
     <s v="Ciencias de la Computación"/>
-    <s v="Keine Übereinstimmung"/>
     <n v="13"/>
+    <s v="Harper"/>
+    <s v="Lee"/>
   </r>
   <r>
     <n v="117"/>
     <s v="Sebastian King"/>
-    <x v="1"/>
-    <s v="C+"/>
+    <s v="History"/>
+    <x v="4"/>
     <s v="Historia"/>
-    <s v="Keine Übereinstimmung"/>
     <n v="10"/>
+    <s v="Sebastian"/>
+    <s v="King"/>
   </r>
   <r>
     <n v="118"/>
     <s v="Evelyn Wright"/>
-    <x v="3"/>
-    <s v="A"/>
+    <s v="Literature"/>
+    <x v="0"/>
     <s v="Literatura"/>
-    <s v="Keine Übereinstimmung"/>
     <n v="15"/>
+    <s v="Evelyn"/>
+    <s v="Wright"/>
   </r>
   <r>
     <n v="119"/>
     <s v="Alexander Scott"/>
-    <x v="4"/>
-    <s v="B-"/>
+    <s v="Chemistry"/>
+    <x v="5"/>
     <s v="Química"/>
-    <s v="Keine Übereinstimmung"/>
     <n v="11"/>
+    <s v="Alexander"/>
+    <s v="Scott"/>
   </r>
   <r>
     <n v="120"/>
     <s v="Scarlett Green"/>
-    <x v="0"/>
-    <s v="A-"/>
+    <s v="Mathematics"/>
+    <x v="2"/>
     <s v="Matemáticas"/>
-    <s v="Keine Übereinstimmung"/>
     <n v="14"/>
+    <s v="Scarlett"/>
+    <s v="Green"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C6AB2001-A89D-4E2C-B80C-DDA982564DE7}" name="PivotTable1" cacheId="2160" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
-  <location ref="A2:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="7">
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A432E051-0BAB-4BA6-A3D4-FE600D5F3120}" name="NotenPivot" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+  <location ref="A4:C12" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
       <items count="8">
-        <item x="5"/>
-        <item x="4"/>
-        <item x="6"/>
-        <item x="1"/>
-        <item x="3"/>
         <item x="0"/>
         <item x="2"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="4"/>
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
-    <field x="2"/>
+    <field x="3"/>
   </rowFields>
   <rowItems count="8">
     <i>
@@ -2027,18 +2351,95 @@
       <x/>
     </i>
   </rowItems>
-  <colItems count="1">
-    <i/>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
   </colItems>
-  <dataFields count="1">
-    <dataField name="Mittelwert von Notenwert" fld="6" subtotal="average" baseField="0" baseItem="0"/>
+  <dataFields count="2">
+    <dataField name="Anzahl Schüler" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Summe Notenwert" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="1">
+  <formats count="6">
+    <format dxfId="17">
+      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="16">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="2">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="15">
+      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="14">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="2">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="13">
+      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="12">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="2">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <chartFormats count="4">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
           </reference>
         </references>
       </pivotArea>
@@ -2057,34 +2458,27 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5FF76944-4563-4FEE-818B-9DB8CB3C0EBE}" name="Tabelle1" displayName="Tabelle1" ref="A1:F21" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="7" tableBorderDxfId="8" totalsRowBorderDxfId="6">
-  <autoFilter ref="A1:F21" xr:uid="{5FF76944-4563-4FEE-818B-9DB8CB3C0EBE}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{D7749C76-6C37-4836-AE04-3BE169132649}" name="Student ID" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{573A9CE7-7A6F-42BC-B1A3-190B6F164F32}" name="Name" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{2181521C-DF81-40F5-A62B-F9C5416D5621}" name="Class" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{4824FCFB-19D4-47FA-9CD7-FC1499734BEA}" name="Grade" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{EE0386E2-9EE9-4DC3-92DF-9E9353F83A97}" name="Class (Espaniol)" dataDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5FF76944-4563-4FEE-818B-9DB8CB3C0EBE}" name="Tabelle1" displayName="Tabelle1" ref="A1:H21" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="A1:H21" xr:uid="{5FF76944-4563-4FEE-818B-9DB8CB3C0EBE}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{D7749C76-6C37-4836-AE04-3BE169132649}" name="Student ID" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{573A9CE7-7A6F-42BC-B1A3-190B6F164F32}" name="Name" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{2181521C-DF81-40F5-A62B-F9C5416D5621}" name="Class" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{4824FCFB-19D4-47FA-9CD7-FC1499734BEA}" name="Grade" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{EE0386E2-9EE9-4DC3-92DF-9E9353F83A97}" name="Class (Espaniol)" dataDxfId="3">
       <calculatedColumnFormula array="1">_xldudf_GPT("übersetze ins spanische",Tabelle1[[#This Row],[Class]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{85536383-F473-4FCB-A971-57920CE080D6}" name="Notenwert" dataDxfId="0">
+    <tableColumn id="7" xr3:uid="{85536383-F473-4FCB-A971-57920CE080D6}" name="Notenwert" dataDxfId="2">
       <calculatedColumnFormula array="1">_xlfn.SWITCH(Tabelle1[[#This Row],[Grade]],"A",15,"A-",14,"B+",13,"B",12,"B-",11,"C+",10,"C",9,0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{3510AFFB-3423-4F80-979C-3C439FD02DC7}" name="Vorname" dataDxfId="1">
+      <calculatedColumnFormula>IFERROR(LEFT(Tabelle1[[#This Row],[Name]],FIND(" ",Tabelle1[[#This Row],[Name]]&amp;" ")-1),Tabelle1[[#This Row],[Name]])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{999D9C80-C0C1-4D8F-AF3C-067B680E0AF9}" name="Nachname" dataDxfId="0">
+      <calculatedColumnFormula>IFERROR(TRIM(MID(Tabelle1[[#This Row],[Name]],FIND(" ",Tabelle1[[#This Row],[Name]]&amp;" ")+1,999)),"")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{38832FDD-FE89-4223-BC45-F94F5F4F5FAC}" name="Tabelle2" displayName="Tabelle2" ref="A1:D10" totalsRowShown="0">
-  <autoFilter ref="A1:D10" xr:uid="{38832FDD-FE89-4223-BC45-F94F5F4F5FAC}"/>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{858DEA7B-A56B-4859-8581-D1FFCCCB5E47}" name="Student ID"/>
-    <tableColumn id="2" xr3:uid="{8674DA8E-FA66-4F4F-B126-D5CBBA409B1E}" name="Name"/>
-    <tableColumn id="3" xr3:uid="{33CC7360-EB6A-4894-90C6-F10DAC45DE0B}" name="Fach"/>
-    <tableColumn id="4" xr3:uid="{6A0F28EB-4B25-401F-8F18-5247C17753C4}" name="Note"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -2405,7 +2799,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="350" row="6">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="4">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -2455,17 +2849,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2788455-9E8A-444A-8C5C-053A6FD450F9}">
-  <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.140625" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="30.75" thickBot="1">
+    <row r="1" spans="1:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -2484,8 +2881,14 @@
       <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="15.75" thickBot="1">
+      <c r="G1" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>101</v>
       </c>
@@ -2506,8 +2909,16 @@
         <f t="array" ref="F2">_xlfn.SWITCH(Tabelle1[[#This Row],[Grade]],"A",15,"A-",14,"B+",13,"B",12,"B-",11,"C+",10,"C",9,0)</f>
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="15.75" thickBot="1">
+      <c r="G2" t="str">
+        <f>IFERROR(LEFT(Tabelle1[[#This Row],[Name]],FIND(" ",Tabelle1[[#This Row],[Name]]&amp;" ")-1),Tabelle1[[#This Row],[Name]])</f>
+        <v>Liam</v>
+      </c>
+      <c r="H2" t="str">
+        <f>IFERROR(TRIM(MID(Tabelle1[[#This Row],[Name]],FIND(" ",Tabelle1[[#This Row],[Name]]&amp;" ")+1,999)),"")</f>
+        <v>Miller</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>102</v>
       </c>
@@ -2528,8 +2939,16 @@
         <f t="array" ref="F3">_xlfn.SWITCH(Tabelle1[[#This Row],[Grade]],"A",15,"A-",14,"B+",13,"B",12,"B-",11,"C+",10,"C",9,0)</f>
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="15.75" thickBot="1">
+      <c r="G3" t="str">
+        <f>IFERROR(LEFT(Tabelle1[[#This Row],[Name]],FIND(" ",Tabelle1[[#This Row],[Name]]&amp;" ")-1),Tabelle1[[#This Row],[Name]])</f>
+        <v>Sophia</v>
+      </c>
+      <c r="H3" t="str">
+        <f>IFERROR(TRIM(MID(Tabelle1[[#This Row],[Name]],FIND(" ",Tabelle1[[#This Row],[Name]]&amp;" ")+1,999)),"")</f>
+        <v>Chen</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>103</v>
       </c>
@@ -2550,8 +2969,16 @@
         <f t="array" ref="F4">_xlfn.SWITCH(Tabelle1[[#This Row],[Grade]],"A",15,"A-",14,"B+",13,"B",12,"B-",11,"C+",10,"C",9,0)</f>
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="15.75" thickBot="1">
+      <c r="G4" t="str">
+        <f>IFERROR(LEFT(Tabelle1[[#This Row],[Name]],FIND(" ",Tabelle1[[#This Row],[Name]]&amp;" ")-1),Tabelle1[[#This Row],[Name]])</f>
+        <v>Noah</v>
+      </c>
+      <c r="H4" t="str">
+        <f>IFERROR(TRIM(MID(Tabelle1[[#This Row],[Name]],FIND(" ",Tabelle1[[#This Row],[Name]]&amp;" ")+1,999)),"")</f>
+        <v>Garcia</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>104</v>
       </c>
@@ -2572,8 +2999,16 @@
         <f t="array" ref="F5">_xlfn.SWITCH(Tabelle1[[#This Row],[Grade]],"A",15,"A-",14,"B+",13,"B",12,"B-",11,"C+",10,"C",9,0)</f>
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="15.75" thickBot="1">
+      <c r="G5" t="str">
+        <f>IFERROR(LEFT(Tabelle1[[#This Row],[Name]],FIND(" ",Tabelle1[[#This Row],[Name]]&amp;" ")-1),Tabelle1[[#This Row],[Name]])</f>
+        <v>Emma</v>
+      </c>
+      <c r="H5" t="str">
+        <f>IFERROR(TRIM(MID(Tabelle1[[#This Row],[Name]],FIND(" ",Tabelle1[[#This Row],[Name]]&amp;" ")+1,999)),"")</f>
+        <v>Wilson</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>105</v>
       </c>
@@ -2594,8 +3029,16 @@
         <f t="array" ref="F6">_xlfn.SWITCH(Tabelle1[[#This Row],[Grade]],"A",15,"A-",14,"B+",13,"B",12,"B-",11,"C+",10,"C",9,0)</f>
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="15.75" thickBot="1">
+      <c r="G6" t="str">
+        <f>IFERROR(LEFT(Tabelle1[[#This Row],[Name]],FIND(" ",Tabelle1[[#This Row],[Name]]&amp;" ")-1),Tabelle1[[#This Row],[Name]])</f>
+        <v>Oliver</v>
+      </c>
+      <c r="H6" t="str">
+        <f>IFERROR(TRIM(MID(Tabelle1[[#This Row],[Name]],FIND(" ",Tabelle1[[#This Row],[Name]]&amp;" ")+1,999)),"")</f>
+        <v>Brown</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>106</v>
       </c>
@@ -2616,8 +3059,16 @@
         <f t="array" ref="F7">_xlfn.SWITCH(Tabelle1[[#This Row],[Grade]],"A",15,"A-",14,"B+",13,"B",12,"B-",11,"C+",10,"C",9,0)</f>
         <v>11</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" ht="15.75" thickBot="1">
+      <c r="G7" t="str">
+        <f>IFERROR(LEFT(Tabelle1[[#This Row],[Name]],FIND(" ",Tabelle1[[#This Row],[Name]]&amp;" ")-1),Tabelle1[[#This Row],[Name]])</f>
+        <v>Ava</v>
+      </c>
+      <c r="H7" t="str">
+        <f>IFERROR(TRIM(MID(Tabelle1[[#This Row],[Name]],FIND(" ",Tabelle1[[#This Row],[Name]]&amp;" ")+1,999)),"")</f>
+        <v>Martinez</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>107</v>
       </c>
@@ -2638,8 +3089,16 @@
         <f t="array" ref="F8">_xlfn.SWITCH(Tabelle1[[#This Row],[Grade]],"A",15,"A-",14,"B+",13,"B",12,"B-",11,"C+",10,"C",9,0)</f>
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" ht="15.75" thickBot="1">
+      <c r="G8" t="str">
+        <f>IFERROR(LEFT(Tabelle1[[#This Row],[Name]],FIND(" ",Tabelle1[[#This Row],[Name]]&amp;" ")-1),Tabelle1[[#This Row],[Name]])</f>
+        <v>Lucas</v>
+      </c>
+      <c r="H8" t="str">
+        <f>IFERROR(TRIM(MID(Tabelle1[[#This Row],[Name]],FIND(" ",Tabelle1[[#This Row],[Name]]&amp;" ")+1,999)),"")</f>
+        <v>Taylor</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>108</v>
       </c>
@@ -2660,8 +3119,16 @@
         <f t="array" ref="F9">_xlfn.SWITCH(Tabelle1[[#This Row],[Grade]],"A",15,"A-",14,"B+",13,"B",12,"B-",11,"C+",10,"C",9,0)</f>
         <v>14</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" ht="15.75" thickBot="1">
+      <c r="G9" t="str">
+        <f>IFERROR(LEFT(Tabelle1[[#This Row],[Name]],FIND(" ",Tabelle1[[#This Row],[Name]]&amp;" ")-1),Tabelle1[[#This Row],[Name]])</f>
+        <v>Mia</v>
+      </c>
+      <c r="H9" t="str">
+        <f>IFERROR(TRIM(MID(Tabelle1[[#This Row],[Name]],FIND(" ",Tabelle1[[#This Row],[Name]]&amp;" ")+1,999)),"")</f>
+        <v>Anderson</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>109</v>
       </c>
@@ -2682,8 +3149,16 @@
         <f t="array" ref="F10">_xlfn.SWITCH(Tabelle1[[#This Row],[Grade]],"A",15,"A-",14,"B+",13,"B",12,"B-",11,"C+",10,"C",9,0)</f>
         <v>12</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="43.5" thickBot="1">
+      <c r="G10" t="str">
+        <f>IFERROR(LEFT(Tabelle1[[#This Row],[Name]],FIND(" ",Tabelle1[[#This Row],[Name]]&amp;" ")-1),Tabelle1[[#This Row],[Name]])</f>
+        <v>Ethan</v>
+      </c>
+      <c r="H10" t="str">
+        <f>IFERROR(TRIM(MID(Tabelle1[[#This Row],[Name]],FIND(" ",Tabelle1[[#This Row],[Name]]&amp;" ")+1,999)),"")</f>
+        <v>Thomas</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>110</v>
       </c>
@@ -2704,8 +3179,16 @@
         <f t="array" ref="F11">_xlfn.SWITCH(Tabelle1[[#This Row],[Grade]],"A",15,"A-",14,"B+",13,"B",12,"B-",11,"C+",10,"C",9,0)</f>
         <v>15</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" ht="15.75" thickBot="1">
+      <c r="G11" t="str">
+        <f>IFERROR(LEFT(Tabelle1[[#This Row],[Name]],FIND(" ",Tabelle1[[#This Row],[Name]]&amp;" ")-1),Tabelle1[[#This Row],[Name]])</f>
+        <v>Isabella</v>
+      </c>
+      <c r="H11" t="str">
+        <f>IFERROR(TRIM(MID(Tabelle1[[#This Row],[Name]],FIND(" ",Tabelle1[[#This Row],[Name]]&amp;" ")+1,999)),"")</f>
+        <v>Moore</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>111</v>
       </c>
@@ -2726,8 +3209,16 @@
         <f t="array" ref="F12">_xlfn.SWITCH(Tabelle1[[#This Row],[Grade]],"A",15,"A-",14,"B+",13,"B",12,"B-",11,"C+",10,"C",9,0)</f>
         <v>9</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" ht="15.75" thickBot="1">
+      <c r="G12" t="str">
+        <f>IFERROR(LEFT(Tabelle1[[#This Row],[Name]],FIND(" ",Tabelle1[[#This Row],[Name]]&amp;" ")-1),Tabelle1[[#This Row],[Name]])</f>
+        <v>Mason</v>
+      </c>
+      <c r="H12" t="str">
+        <f>IFERROR(TRIM(MID(Tabelle1[[#This Row],[Name]],FIND(" ",Tabelle1[[#This Row],[Name]]&amp;" ")+1,999)),"")</f>
+        <v>Jackson</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>112</v>
       </c>
@@ -2748,8 +3239,16 @@
         <f t="array" ref="F13">_xlfn.SWITCH(Tabelle1[[#This Row],[Grade]],"A",15,"A-",14,"B+",13,"B",12,"B-",11,"C+",10,"C",9,0)</f>
         <v>13</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" ht="15.75" thickBot="1">
+      <c r="G13" t="str">
+        <f>IFERROR(LEFT(Tabelle1[[#This Row],[Name]],FIND(" ",Tabelle1[[#This Row],[Name]]&amp;" ")-1),Tabelle1[[#This Row],[Name]])</f>
+        <v>Charlotte</v>
+      </c>
+      <c r="H13" t="str">
+        <f>IFERROR(TRIM(MID(Tabelle1[[#This Row],[Name]],FIND(" ",Tabelle1[[#This Row],[Name]]&amp;" ")+1,999)),"")</f>
+        <v>White</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>113</v>
       </c>
@@ -2770,8 +3269,16 @@
         <f t="array" ref="F14">_xlfn.SWITCH(Tabelle1[[#This Row],[Grade]],"A",15,"A-",14,"B+",13,"B",12,"B-",11,"C+",10,"C",9,0)</f>
         <v>15</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" ht="15.75" thickBot="1">
+      <c r="G14" t="str">
+        <f>IFERROR(LEFT(Tabelle1[[#This Row],[Name]],FIND(" ",Tabelle1[[#This Row],[Name]]&amp;" ")-1),Tabelle1[[#This Row],[Name]])</f>
+        <v>James</v>
+      </c>
+      <c r="H14" t="str">
+        <f>IFERROR(TRIM(MID(Tabelle1[[#This Row],[Name]],FIND(" ",Tabelle1[[#This Row],[Name]]&amp;" ")+1,999)),"")</f>
+        <v>Harris</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>114</v>
       </c>
@@ -2792,8 +3299,16 @@
         <f t="array" ref="F15">_xlfn.SWITCH(Tabelle1[[#This Row],[Grade]],"A",15,"A-",14,"B+",13,"B",12,"B-",11,"C+",10,"C",9,0)</f>
         <v>12</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" ht="15.75" thickBot="1">
+      <c r="G15" t="str">
+        <f>IFERROR(LEFT(Tabelle1[[#This Row],[Name]],FIND(" ",Tabelle1[[#This Row],[Name]]&amp;" ")-1),Tabelle1[[#This Row],[Name]])</f>
+        <v>Amelia</v>
+      </c>
+      <c r="H15" t="str">
+        <f>IFERROR(TRIM(MID(Tabelle1[[#This Row],[Name]],FIND(" ",Tabelle1[[#This Row],[Name]]&amp;" ")+1,999)),"")</f>
+        <v>Martin</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>115</v>
       </c>
@@ -2814,8 +3329,16 @@
         <f t="array" ref="F16">_xlfn.SWITCH(Tabelle1[[#This Row],[Grade]],"A",15,"A-",14,"B+",13,"B",12,"B-",11,"C+",10,"C",9,0)</f>
         <v>14</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" ht="43.5" thickBot="1">
+      <c r="G16" t="str">
+        <f>IFERROR(LEFT(Tabelle1[[#This Row],[Name]],FIND(" ",Tabelle1[[#This Row],[Name]]&amp;" ")-1),Tabelle1[[#This Row],[Name]])</f>
+        <v>Benjamin</v>
+      </c>
+      <c r="H16" t="str">
+        <f>IFERROR(TRIM(MID(Tabelle1[[#This Row],[Name]],FIND(" ",Tabelle1[[#This Row],[Name]]&amp;" ")+1,999)),"")</f>
+        <v>Thompson</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>116</v>
       </c>
@@ -2836,8 +3359,16 @@
         <f t="array" ref="F17">_xlfn.SWITCH(Tabelle1[[#This Row],[Grade]],"A",15,"A-",14,"B+",13,"B",12,"B-",11,"C+",10,"C",9,0)</f>
         <v>13</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" ht="15.75" thickBot="1">
+      <c r="G17" t="str">
+        <f>IFERROR(LEFT(Tabelle1[[#This Row],[Name]],FIND(" ",Tabelle1[[#This Row],[Name]]&amp;" ")-1),Tabelle1[[#This Row],[Name]])</f>
+        <v>Harper</v>
+      </c>
+      <c r="H17" t="str">
+        <f>IFERROR(TRIM(MID(Tabelle1[[#This Row],[Name]],FIND(" ",Tabelle1[[#This Row],[Name]]&amp;" ")+1,999)),"")</f>
+        <v>Lee</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>117</v>
       </c>
@@ -2858,8 +3389,16 @@
         <f t="array" ref="F18">_xlfn.SWITCH(Tabelle1[[#This Row],[Grade]],"A",15,"A-",14,"B+",13,"B",12,"B-",11,"C+",10,"C",9,0)</f>
         <v>10</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" ht="15.75" thickBot="1">
+      <c r="G18" t="str">
+        <f>IFERROR(LEFT(Tabelle1[[#This Row],[Name]],FIND(" ",Tabelle1[[#This Row],[Name]]&amp;" ")-1),Tabelle1[[#This Row],[Name]])</f>
+        <v>Sebastian</v>
+      </c>
+      <c r="H18" t="str">
+        <f>IFERROR(TRIM(MID(Tabelle1[[#This Row],[Name]],FIND(" ",Tabelle1[[#This Row],[Name]]&amp;" ")+1,999)),"")</f>
+        <v>King</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>118</v>
       </c>
@@ -2880,8 +3419,16 @@
         <f t="array" ref="F19">_xlfn.SWITCH(Tabelle1[[#This Row],[Grade]],"A",15,"A-",14,"B+",13,"B",12,"B-",11,"C+",10,"C",9,0)</f>
         <v>15</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" ht="15.75" thickBot="1">
+      <c r="G19" t="str">
+        <f>IFERROR(LEFT(Tabelle1[[#This Row],[Name]],FIND(" ",Tabelle1[[#This Row],[Name]]&amp;" ")-1),Tabelle1[[#This Row],[Name]])</f>
+        <v>Evelyn</v>
+      </c>
+      <c r="H19" t="str">
+        <f>IFERROR(TRIM(MID(Tabelle1[[#This Row],[Name]],FIND(" ",Tabelle1[[#This Row],[Name]]&amp;" ")+1,999)),"")</f>
+        <v>Wright</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>119</v>
       </c>
@@ -2902,8 +3449,16 @@
         <f t="array" ref="F20">_xlfn.SWITCH(Tabelle1[[#This Row],[Grade]],"A",15,"A-",14,"B+",13,"B",12,"B-",11,"C+",10,"C",9,0)</f>
         <v>11</v>
       </c>
-    </row>
-    <row r="21" spans="1:6">
+      <c r="G20" t="str">
+        <f>IFERROR(LEFT(Tabelle1[[#This Row],[Name]],FIND(" ",Tabelle1[[#This Row],[Name]]&amp;" ")-1),Tabelle1[[#This Row],[Name]])</f>
+        <v>Alexander</v>
+      </c>
+      <c r="H20" t="str">
+        <f>IFERROR(TRIM(MID(Tabelle1[[#This Row],[Name]],FIND(" ",Tabelle1[[#This Row],[Name]]&amp;" ")+1,999)),"")</f>
+        <v>Scott</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>120</v>
       </c>
@@ -2923,6 +3478,14 @@
       <c r="F21" cm="1">
         <f t="array" ref="F21">_xlfn.SWITCH(Tabelle1[[#This Row],[Grade]],"A",15,"A-",14,"B+",13,"B",12,"B-",11,"C+",10,"C",9,0)</f>
         <v>14</v>
+      </c>
+      <c r="G21" t="str">
+        <f>IFERROR(LEFT(Tabelle1[[#This Row],[Name]],FIND(" ",Tabelle1[[#This Row],[Name]]&amp;" ")-1),Tabelle1[[#This Row],[Name]])</f>
+        <v>Scarlett</v>
+      </c>
+      <c r="H21" t="str">
+        <f>IFERROR(TRIM(MID(Tabelle1[[#This Row],[Name]],FIND(" ",Tabelle1[[#This Row],[Name]]&amp;" ")+1,999)),"")</f>
+        <v>Green</v>
       </c>
     </row>
   </sheetData>
@@ -2934,199 +3497,43 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97BDDBC9-1110-4D7F-BA35-2C2AAFB0A1FB}">
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2">
-        <v>101</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3">
-        <v>103</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4">
-        <v>107</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5">
-        <v>108</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6">
-        <v>110</v>
-      </c>
-      <c r="B6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7">
-        <v>113</v>
-      </c>
-      <c r="B7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8">
-        <v>115</v>
-      </c>
-      <c r="B8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9">
-        <v>118</v>
-      </c>
-      <c r="B9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10">
-        <v>120</v>
-      </c>
-      <c r="B10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" t="s">
-        <v>42</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D95CC1EB-A70C-4E03-AC49-200FA36B1578}">
   <dimension ref="ACB10118:WWX918056"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="10118" spans="14559:14559">
+    <row r="10118" spans="14559:14559" x14ac:dyDescent="0.25">
       <c r="UMY10118" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="216670" spans="16170:16170" x14ac:dyDescent="0.25">
+      <c r="WWX216670" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="274598" spans="8002:8002" x14ac:dyDescent="0.25">
+      <c r="KUT274598" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="467039" spans="10179:10179" x14ac:dyDescent="0.25">
+      <c r="OAM467039" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="216670" spans="16170:16170">
-      <c r="WWX216670" t="s">
+    <row r="602532" spans="756:756" x14ac:dyDescent="0.25">
+      <c r="ACB602532" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="274598" spans="8002:8002">
-      <c r="KUT274598" t="s">
+    <row r="755272" spans="12075:12075" x14ac:dyDescent="0.25">
+      <c r="QVK755272" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="467039" spans="10179:10179">
-      <c r="OAM467039" t="s">
+    <row r="918056" spans="9317:9317" x14ac:dyDescent="0.25">
+      <c r="MTI918056" t="s">
         <v>46</v>
-      </c>
-    </row>
-    <row r="602532" spans="756:756">
-      <c r="ACB602532" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="755272" spans="12075:12075">
-      <c r="QVK755272" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="918056" spans="9317:9317">
-      <c r="MTI918056" t="s">
-        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -3134,85 +3541,145 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23A83D4B-E750-4EAF-A541-CC17AE316112}">
-  <dimension ref="A2:B10"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5338A566-B8A3-4C40-A4FF-57B77C1482E3}">
+  <dimension ref="A1:L12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="56.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2">
-      <c r="A2" s="11" t="s">
+    <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3">
-        <v>13.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4">
-        <v>11.333333333333334</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6">
-        <v>12.333333333333334</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>13.75</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>13</v>
+      <c r="C8">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
+        <v>11</v>
       </c>
       <c r="B9">
-        <v>13.333333333333334</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
-        <v>51</v>
+        <v>3</v>
+      </c>
+      <c r="C9">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
+        <v>30</v>
       </c>
       <c r="B10">
-        <v>12.85</v>
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12">
+        <v>20</v>
+      </c>
+      <c r="C12">
+        <v>257</v>
       </c>
     </row>
   </sheetData>
